--- a/data/analysis/momentumImproved/mergeTtestResult/tTestReport-201001_202412_p.xlsx
+++ b/data/analysis/momentumImproved/mergeTtestResult/tTestReport-201001_202412_p.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="104">
   <si>
     <t>J=</t>
   </si>
@@ -43,286 +43,289 @@
     <t>winner - loser</t>
   </si>
   <si>
-    <t>11.55%</t>
-  </si>
-  <si>
-    <t>(6.91)</t>
-  </si>
-  <si>
-    <t>9.47%</t>
-  </si>
-  <si>
-    <t>(5.63)</t>
-  </si>
-  <si>
-    <t>-2.08%</t>
-  </si>
-  <si>
-    <t>(-1.81)</t>
-  </si>
-  <si>
-    <t>5.52%</t>
-  </si>
-  <si>
-    <t>(3.62)</t>
-  </si>
-  <si>
-    <t>11.95%</t>
-  </si>
-  <si>
-    <t>(7.50)</t>
-  </si>
-  <si>
-    <t>6.43%</t>
-  </si>
-  <si>
-    <t>(7.17)</t>
-  </si>
-  <si>
-    <t>6.75%</t>
-  </si>
-  <si>
-    <t>(4.22)</t>
-  </si>
-  <si>
-    <t>11.63%</t>
-  </si>
-  <si>
-    <t>(6.87)</t>
-  </si>
-  <si>
-    <t>4.88%</t>
-  </si>
-  <si>
-    <t>(5.29)</t>
-  </si>
-  <si>
-    <t>8.67%</t>
-  </si>
-  <si>
-    <t>(5.23)</t>
-  </si>
-  <si>
-    <t>10.11%</t>
-  </si>
-  <si>
-    <t>(6.00)</t>
-  </si>
-  <si>
-    <t>1.43%</t>
-  </si>
-  <si>
-    <t>(1.45)</t>
-  </si>
-  <si>
-    <t>1.31%</t>
-  </si>
-  <si>
-    <t>(1.52)</t>
-  </si>
-  <si>
-    <t>2.99%</t>
-  </si>
-  <si>
-    <t>(3.66)</t>
-  </si>
-  <si>
-    <t>1.67%</t>
-  </si>
-  <si>
-    <t>(2.99)</t>
-  </si>
-  <si>
-    <t>0.90%</t>
-  </si>
-  <si>
-    <t>(1.13)</t>
-  </si>
-  <si>
-    <t>3.65%</t>
-  </si>
-  <si>
-    <t>(4.93)</t>
-  </si>
-  <si>
-    <t>2.75%</t>
-  </si>
-  <si>
-    <t>(5.49)</t>
-  </si>
-  <si>
-    <t>0.84%</t>
-  </si>
-  <si>
-    <t>(1.02)</t>
-  </si>
-  <si>
-    <t>3.77%</t>
-  </si>
-  <si>
-    <t>(4.81)</t>
-  </si>
-  <si>
-    <t>2.93%</t>
-  </si>
-  <si>
-    <t>(5.33)</t>
-  </si>
-  <si>
-    <t>0.77%</t>
-  </si>
-  <si>
-    <t>(0.90)</t>
-  </si>
-  <si>
-    <t>3.78%</t>
-  </si>
-  <si>
-    <t>(4.79)</t>
-  </si>
-  <si>
-    <t>3.01%</t>
-  </si>
-  <si>
-    <t>(5.35)</t>
-  </si>
-  <si>
-    <t>3.84%</t>
-  </si>
-  <si>
-    <t>(3.40)</t>
-  </si>
-  <si>
-    <t>5.65%</t>
-  </si>
-  <si>
-    <t>(4.96)</t>
-  </si>
-  <si>
-    <t>1.81%</t>
-  </si>
-  <si>
-    <t>(2.45)</t>
-  </si>
-  <si>
-    <t>1.92%</t>
-  </si>
-  <si>
-    <t>(1.93)</t>
-  </si>
-  <si>
-    <t>7.15%</t>
-  </si>
-  <si>
-    <t>(6.70)</t>
-  </si>
-  <si>
-    <t>5.23%</t>
-  </si>
-  <si>
-    <t>(8.56)</t>
-  </si>
-  <si>
-    <t>1.80%</t>
-  </si>
-  <si>
-    <t>(1.72)</t>
-  </si>
-  <si>
-    <t>7.46%</t>
-  </si>
-  <si>
-    <t>(6.80)</t>
-  </si>
-  <si>
-    <t>5.66%</t>
-  </si>
-  <si>
-    <t>(8.47)</t>
-  </si>
-  <si>
-    <t>2.35%</t>
-  </si>
-  <si>
-    <t>(2.10)</t>
-  </si>
-  <si>
-    <t>6.79%</t>
-  </si>
-  <si>
-    <t>(6.30)</t>
-  </si>
-  <si>
-    <t>4.44%</t>
-  </si>
-  <si>
-    <t>(6.50)</t>
-  </si>
-  <si>
-    <t>7.03%</t>
-  </si>
-  <si>
-    <t>(5.08)</t>
-  </si>
-  <si>
-    <t>7.47%</t>
-  </si>
-  <si>
-    <t>(5.38)</t>
-  </si>
-  <si>
-    <t>0.44%</t>
-  </si>
-  <si>
-    <t>(0.49)</t>
-  </si>
-  <si>
-    <t>3.16%</t>
-  </si>
-  <si>
-    <t>(2.60)</t>
-  </si>
-  <si>
-    <t>9.99%</t>
-  </si>
-  <si>
-    <t>(7.72)</t>
-  </si>
-  <si>
-    <t>6.83%</t>
-  </si>
-  <si>
-    <t>(8.88)</t>
-  </si>
-  <si>
-    <t>3.67%</t>
-  </si>
-  <si>
-    <t>(2.88)</t>
-  </si>
-  <si>
-    <t>(7.34)</t>
-  </si>
-  <si>
-    <t>6.32%</t>
-  </si>
-  <si>
-    <t>(8.21)</t>
-  </si>
-  <si>
-    <t>4.81%</t>
-  </si>
-  <si>
-    <t>(3.59)</t>
-  </si>
-  <si>
-    <t>8.79%</t>
-  </si>
-  <si>
-    <t>3.98%</t>
-  </si>
-  <si>
-    <t>(4.95)</t>
+    <t>0.1155</t>
+  </si>
+  <si>
+    <t>6.9121</t>
+  </si>
+  <si>
+    <t>0.0947</t>
+  </si>
+  <si>
+    <t>5.6286</t>
+  </si>
+  <si>
+    <t>-0.0208</t>
+  </si>
+  <si>
+    <t>-1.8145</t>
+  </si>
+  <si>
+    <t>0.0552</t>
+  </si>
+  <si>
+    <t>3.6216</t>
+  </si>
+  <si>
+    <t>0.1195</t>
+  </si>
+  <si>
+    <t>7.5033</t>
+  </si>
+  <si>
+    <t>0.0643</t>
+  </si>
+  <si>
+    <t>7.1660</t>
+  </si>
+  <si>
+    <t>0.0675</t>
+  </si>
+  <si>
+    <t>4.2244</t>
+  </si>
+  <si>
+    <t>0.1163</t>
+  </si>
+  <si>
+    <t>6.8672</t>
+  </si>
+  <si>
+    <t>0.0488</t>
+  </si>
+  <si>
+    <t>5.2915</t>
+  </si>
+  <si>
+    <t>0.0867</t>
+  </si>
+  <si>
+    <t>5.2321</t>
+  </si>
+  <si>
+    <t>0.1011</t>
+  </si>
+  <si>
+    <t>6.0029</t>
+  </si>
+  <si>
+    <t>0.0143</t>
+  </si>
+  <si>
+    <t>1.4471</t>
+  </si>
+  <si>
+    <t>0.0131</t>
+  </si>
+  <si>
+    <t>1.5165</t>
+  </si>
+  <si>
+    <t>0.0299</t>
+  </si>
+  <si>
+    <t>3.6570</t>
+  </si>
+  <si>
+    <t>0.0167</t>
+  </si>
+  <si>
+    <t>2.9943</t>
+  </si>
+  <si>
+    <t>0.0090</t>
+  </si>
+  <si>
+    <t>1.1263</t>
+  </si>
+  <si>
+    <t>0.0365</t>
+  </si>
+  <si>
+    <t>4.9316</t>
+  </si>
+  <si>
+    <t>0.0275</t>
+  </si>
+  <si>
+    <t>5.4890</t>
+  </si>
+  <si>
+    <t>0.0084</t>
+  </si>
+  <si>
+    <t>1.0175</t>
+  </si>
+  <si>
+    <t>0.0377</t>
+  </si>
+  <si>
+    <t>4.8078</t>
+  </si>
+  <si>
+    <t>0.0293</t>
+  </si>
+  <si>
+    <t>5.3341</t>
+  </si>
+  <si>
+    <t>0.0077</t>
+  </si>
+  <si>
+    <t>0.9029</t>
+  </si>
+  <si>
+    <t>0.0378</t>
+  </si>
+  <si>
+    <t>4.7869</t>
+  </si>
+  <si>
+    <t>0.0301</t>
+  </si>
+  <si>
+    <t>5.3463</t>
+  </si>
+  <si>
+    <t>0.0384</t>
+  </si>
+  <si>
+    <t>3.4033</t>
+  </si>
+  <si>
+    <t>0.0565</t>
+  </si>
+  <si>
+    <t>4.9596</t>
+  </si>
+  <si>
+    <t>0.0181</t>
+  </si>
+  <si>
+    <t>2.4462</t>
+  </si>
+  <si>
+    <t>0.0192</t>
+  </si>
+  <si>
+    <t>1.9344</t>
+  </si>
+  <si>
+    <t>0.0715</t>
+  </si>
+  <si>
+    <t>6.7041</t>
+  </si>
+  <si>
+    <t>0.0523</t>
+  </si>
+  <si>
+    <t>8.5640</t>
+  </si>
+  <si>
+    <t>0.0180</t>
+  </si>
+  <si>
+    <t>1.7225</t>
+  </si>
+  <si>
+    <t>0.0746</t>
+  </si>
+  <si>
+    <t>6.7980</t>
+  </si>
+  <si>
+    <t>0.0566</t>
+  </si>
+  <si>
+    <t>8.4659</t>
+  </si>
+  <si>
+    <t>0.0235</t>
+  </si>
+  <si>
+    <t>2.1020</t>
+  </si>
+  <si>
+    <t>0.0679</t>
+  </si>
+  <si>
+    <t>6.3015</t>
+  </si>
+  <si>
+    <t>0.0444</t>
+  </si>
+  <si>
+    <t>6.4967</t>
+  </si>
+  <si>
+    <t>0.0703</t>
+  </si>
+  <si>
+    <t>5.0800</t>
+  </si>
+  <si>
+    <t>0.0747</t>
+  </si>
+  <si>
+    <t>5.3826</t>
+  </si>
+  <si>
+    <t>0.0044</t>
+  </si>
+  <si>
+    <t>0.4940</t>
+  </si>
+  <si>
+    <t>0.0316</t>
+  </si>
+  <si>
+    <t>2.6015</t>
+  </si>
+  <si>
+    <t>0.0999</t>
+  </si>
+  <si>
+    <t>7.7216</t>
+  </si>
+  <si>
+    <t>0.0683</t>
+  </si>
+  <si>
+    <t>8.8782</t>
+  </si>
+  <si>
+    <t>0.0367</t>
+  </si>
+  <si>
+    <t>2.8769</t>
+  </si>
+  <si>
+    <t>7.3401</t>
+  </si>
+  <si>
+    <t>0.0632</t>
+  </si>
+  <si>
+    <t>8.2097</t>
+  </si>
+  <si>
+    <t>0.0481</t>
+  </si>
+  <si>
+    <t>3.5855</t>
+  </si>
+  <si>
+    <t>0.0879</t>
+  </si>
+  <si>
+    <t>6.4996</t>
+  </si>
+  <si>
+    <t>0.0398</t>
+  </si>
+  <si>
+    <t>4.9546</t>
   </si>
 </sst>
 </file>
@@ -1074,7 +1077,7 @@
         <v>78</v>
       </c>
       <c r="F23" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1094,7 +1097,7 @@
         <v>79</v>
       </c>
       <c r="F24" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1108,7 +1111,7 @@
         <v>80</v>
       </c>
       <c r="F25" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
